--- a/Example.xlsx
+++ b/Example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MDMSMCVRP\Version 5\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDA64F4-B9F9-40C0-884F-1FAA8B628849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754320EE-6677-4576-AFF5-6D4AC758B3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{993669B2-51F8-400C-BAC3-65C59478D3AC}"/>
   </bookViews>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -611,13 +611,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>3000</v>
       </c>
       <c r="D3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -658,13 +658,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -787,10 +787,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D7">
         <v>2000</v>
@@ -837,10 +837,10 @@
         <v>2000</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D8">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
@@ -860,10 +860,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C9">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="D9">
         <v>2000</v>
@@ -1052,13 +1052,13 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C12">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D12">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="L12" t="s">
         <v>10</v>
@@ -1108,13 +1108,13 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="D13">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
@@ -1164,13 +1164,13 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="C14">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="D14">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="L14" t="s">
         <v>21</v>
@@ -1323,10 +1323,10 @@
         <v>1000</v>
       </c>
       <c r="C17">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D17">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="s">
         <v>24</v>
@@ -1376,10 +1376,10 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C18">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="D18">
         <v>1000</v>
@@ -1438,7 +1438,7 @@
         <v>1000</v>
       </c>
       <c r="D19">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
